--- a/filer_2/13590400_jysk_a_s.xlsx
+++ b/filer_2/13590400_jysk_a_s.xlsx
@@ -4608,9 +4608,15 @@
       <c r="C15" s="16" t="n">
         <v>17257</v>
       </c>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="D15" s="16" t="n">
+        <v>-10858</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>19186</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>24203</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
